--- a/assets/kras-registration-helper-template.xlsx
+++ b/assets/kras-registration-helper-template.xlsx
@@ -1141,11 +1141,14 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://kras.kosha.or.kr/</t>
+          <t>https://portal.kosha.or.kr/kras/implement/real</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/assets/kras-registration-helper-template.xlsx
+++ b/assets/kras-registration-helper-template.xlsx
@@ -1064,7 +1064,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025 KRAS 사용설명서에서는 일반 3단계/체크리스트/OPS/빈도강도 평가의 Excel 일괄 직접 업로드 기능을 명시적으로 확인할 수 없어 직접 업로드 호환을 보장하지 않습니다.</t>
+          <t>KRAS 사용설명서에서는 일반 3단계/체크리스트/OPS/빈도강도 평가의 Excel 일괄 직접 업로드 기능을 명시적으로 확인할 수 없어 직접 업로드 호환을 보장하지 않습니다.</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
